--- a/django/camac/statistics/config/kt_ag/work-items_service-afb.xlsx
+++ b/django/camac/statistics/config/kt_ag/work-items_service-afb.xlsx
@@ -8,27 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D7DEDA1-A68D-4173-9AC6-BA6FDFB90A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E11436B-A41B-4983-AC6E-A1FCA7D705BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="31755" windowHeight="16770" tabRatio="816" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="22485" windowHeight="20430" tabRatio="816" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
     <sheet name="Anzahl" sheetId="7" r:id="rId2"/>
     <sheet name="Aktiv Durchlaufzeit pro PL" sheetId="8" r:id="rId3"/>
     <sheet name="Aktiv Fristgerecht pro PL" sheetId="9" r:id="rId4"/>
-    <sheet name="Controlling Rolle Fristgerecht" sheetId="10" r:id="rId5"/>
-    <sheet name="Controlling Durchlaufzeit FS" sheetId="11" r:id="rId6"/>
+    <sheet name="Aktiv Fristgerecht PL Aufgabe" sheetId="12" r:id="rId5"/>
+    <sheet name="Controlling Rolle Fristgerecht" sheetId="10" r:id="rId6"/>
+    <sheet name="Controlling Durchlaufzeit FS" sheetId="11" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="56" r:id="rId7"/>
+    <pivotCache cacheId="61" r:id="rId8"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="32">
   <si>
     <t>Dossier-Nr.</t>
   </si>
@@ -75,9 +76,6 @@
     <t>Fristgerecht</t>
   </si>
   <si>
-    <t>Spaltenbeschriftungen</t>
-  </si>
-  <si>
     <t>(Leer)</t>
   </si>
   <si>
@@ -97,13 +95,46 @@
   </si>
   <si>
     <t>Anzahl von Dossier-Nr.</t>
+  </si>
+  <si>
+    <t>Anzahl</t>
+  </si>
+  <si>
+    <t>Anteil</t>
+  </si>
+  <si>
+    <t>Anzahl fristgerecht erledigte Aufgaben pro zuständige Person</t>
+  </si>
+  <si>
+    <t>Fristgerecht-Filter</t>
+  </si>
+  <si>
+    <t>Zuständige Person</t>
+  </si>
+  <si>
+    <t>Anzahl fristgerecht erledigte Aufgaben AfB</t>
+  </si>
+  <si>
+    <t>Rolle</t>
+  </si>
+  <si>
+    <t>Anzahl fristgerecht erledigte Aufgaben pro zuständige Person nach Aufgabentyp</t>
+  </si>
+  <si>
+    <t>Anzahl Dossiers</t>
+  </si>
+  <si>
+    <t>Durchschnittliche Durchlaufzeit Aufgaben pro zuständige Person</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -115,6 +146,19 @@
       <b/>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -137,26 +181,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="1">
     <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -172,7 +215,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Stoppe Tilo  Extern" refreshedDate="46111.702895254632" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="1" xr:uid="{A57ED19D-C755-44C2-B72B-40B118E6169D}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Stoppe Tilo  Extern" refreshedDate="46122.594541666665" missingItemsLimit="0" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="19" xr:uid="{A57ED19D-C755-44C2-B72B-40B118E6169D}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:O1048576" sheet="Data"/>
   </cacheSource>
@@ -196,7 +239,9 @@
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
     <cacheField name="Aufgabe" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1" count="1">
+        <m/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Erstellt am" numFmtId="0">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
@@ -208,17 +253,13 @@
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
     <cacheField name="Zuständiger Benutzer" numFmtId="0">
-      <sharedItems containsNonDate="0" containsBlank="1" count="3">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1" count="1">
         <m/>
-        <s v="Max M" u="1"/>
-        <s v="Peter K" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Zuständige Rolle" numFmtId="0">
-      <sharedItems containsNonDate="0" containsBlank="1" count="3">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1" count="1">
         <m/>
-        <s v="AfB" u="1"/>
-        <s v="Denkmalschutz" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Status" numFmtId="0">
@@ -228,10 +269,8 @@
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
     <cacheField name="Fristgerecht" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="1" count="3">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1" count="1">
         <m/>
-        <n v="1" u="1"/>
-        <n v="0" u="1"/>
       </sharedItems>
     </cacheField>
   </cacheFields>
@@ -244,7 +283,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="1">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="19">
   <r>
     <m/>
     <m/>
@@ -252,7 +291,313 @@
     <m/>
     <m/>
     <m/>
-    <m/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
     <m/>
     <m/>
     <m/>
@@ -266,7 +611,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AD818D30-AE36-4ACB-A861-394F5C307186}" name="PivotTable3" cacheId="56" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AD818D30-AE36-4ACB-A861-394F5C307186}" name="PivotTable3" cacheId="61" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:A4" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="15">
     <pivotField dataField="1" showAll="0"/>
@@ -307,7 +652,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47A99F71-D715-4130-9576-1DA447D613A1}" name="PivotTable4" cacheId="56" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47A99F71-D715-4130-9576-1DA447D613A1}" name="PivotTable4" cacheId="61" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -321,10 +666,8 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="4">
+      <items count="2">
         <item x="0"/>
-        <item m="1" x="1"/>
-        <item m="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -348,14 +691,14 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Mittelwert von Durchlaufzeit" fld="13" subtotal="average" baseField="10" baseItem="0"/>
+    <dataField name="Mittelwert von Durchlaufzeit" fld="13" subtotal="average" baseField="10" baseItem="0" numFmtId="1"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="1">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+    <format dxfId="0">
+      <pivotArea outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="10" count="1">
-            <x v="1"/>
+          <reference field="4294967294" count="1">
+            <x v="0"/>
           </reference>
         </references>
       </pivotArea>
@@ -374,8 +717,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{152CAD33-7C43-4DE9-8D77-65A9809A8351}" name="PivotTable5" cacheId="56" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:C6" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{152CAD33-7C43-4DE9-8D77-65A9809A8351}" name="PivotTable5" cacheId="61" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Fristgerecht-Filter">
+  <location ref="A3:E7" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
@@ -388,9 +731,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item m="1" x="1"/>
-        <item m="1" x="2"/>
+      <items count="2">
         <item x="0"/>
         <item t="default"/>
       </items>
@@ -399,10 +740,8 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item n="Nicht fristgerecht" m="1" x="2"/>
-        <item n="fristgerecht" m="1" x="1"/>
-        <item h="1" x="0"/>
+      <items count="2">
+        <item x="0"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -410,7 +749,10 @@
   <rowFields count="1">
     <field x="10"/>
   </rowFields>
-  <rowItems count="1">
+  <rowItems count="2">
+    <i>
+      <x/>
+    </i>
     <i t="grand">
       <x/>
     </i>
@@ -419,12 +761,19 @@
     <field x="14"/>
     <field x="-2"/>
   </colFields>
-  <colItems count="2">
+  <colItems count="4">
+    <i>
+      <x/>
+      <x/>
+    </i>
+    <i r="1" i="1">
+      <x v="1"/>
+    </i>
     <i t="grand">
       <x/>
     </i>
     <i t="grand" i="1">
-      <x v="1"/>
+      <x/>
     </i>
   </colItems>
   <dataFields count="2">
@@ -444,8 +793,76 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C35527E3-4E41-4635-ACA8-0C5A7744445B}" name="PivotTable6" cacheId="56" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:C6" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C25041AB-465F-4D59-A0D5-A4DCE7C22BCC}" name="PivotTable1" cacheId="61" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Fristgerecht-Filter">
+  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
+  <pivotFields count="15">
+    <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisCol" showAll="0" defaultSubtotal="0">
+      <items count="1">
+        <item x="0"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisRow" showAll="0" defaultSubtotal="0">
+      <items count="1">
+        <item x="0"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisCol" showAll="0" defaultSubtotal="0">
+      <items count="1">
+        <item x="0"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="10"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="2">
+    <field x="14"/>
+    <field x="6"/>
+  </colFields>
+  <colItems count="1">
+    <i>
+      <x/>
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Anzahl Dossiers" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C35527E3-4E41-4635-ACA8-0C5A7744445B}" name="PivotTable6" cacheId="61" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Rolle" colHeaderCaption="Fristgerecht-Filter">
+  <location ref="A3:E7" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
@@ -459,20 +876,16 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="4">
+      <items count="2">
         <item x="0"/>
-        <item m="1" x="1"/>
-        <item m="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item n="Nicht Fristgerecht" m="1" x="2"/>
-        <item n="Fristgerecht" m="1" x="1"/>
-        <item h="1" x="0"/>
+      <items count="2">
+        <item x="0"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -480,7 +893,10 @@
   <rowFields count="1">
     <field x="11"/>
   </rowFields>
-  <rowItems count="1">
+  <rowItems count="2">
+    <i>
+      <x/>
+    </i>
     <i t="grand">
       <x/>
     </i>
@@ -489,12 +905,19 @@
     <field x="14"/>
     <field x="-2"/>
   </colFields>
-  <colItems count="2">
+  <colItems count="4">
+    <i>
+      <x/>
+      <x/>
+    </i>
+    <i r="1" i="1">
+      <x v="1"/>
+    </i>
     <i t="grand">
       <x/>
     </i>
     <i t="grand" i="1">
-      <x v="1"/>
+      <x/>
     </i>
   </colItems>
   <dataFields count="2">
@@ -513,8 +936,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{920585A1-89C8-48F8-85AC-53EA3CF3C46A}" name="PivotTable7" cacheId="56" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{920585A1-89C8-48F8-85AC-53EA3CF3C46A}" name="PivotTable7" cacheId="61" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Rolle">
   <location ref="A3:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -529,9 +952,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item m="1" x="1"/>
-        <item m="1" x="2"/>
+      <items count="2">
         <item x="0"/>
         <item t="default"/>
       </items>
@@ -545,7 +966,7 @@
   </rowFields>
   <rowItems count="2">
     <i>
-      <x v="2"/>
+      <x/>
     </i>
     <i t="grand">
       <x/>
@@ -555,7 +976,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Mittelwert von Durchlaufzeit" fld="13" subtotal="average" baseField="11" baseItem="0" numFmtId="2"/>
+    <dataField name="Mittelwert von Durchlaufzeit" fld="13" subtotal="average" baseField="11" baseItem="0" numFmtId="1"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -886,7 +1307,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -897,7 +1318,7 @@
     <col min="6" max="6" width="10" customWidth="1"/>
     <col min="7" max="7" width="9" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="7" customWidth="1"/>
+    <col min="9" max="9" width="11" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
     <col min="11" max="11" width="22" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
@@ -907,53 +1328,162 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
     </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+    </row>
+    <row r="17" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+    </row>
+    <row r="18" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+    </row>
+    <row r="19" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -968,11 +1498,11 @@
   <sheetData>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6"/>
+      <c r="A4" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -981,32 +1511,37 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6568A324-175D-4B52-B017-796124AF40DD}">
-  <dimension ref="A3:B5"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="6"/>
+        <v>15</v>
+      </c>
+      <c r="B4" s="8"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="6"/>
+        <v>19</v>
+      </c>
+      <c r="B5" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1015,44 +1550,75 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FDB89C4-4A7C-4379-BAAC-67A7DE22B254}">
-  <dimension ref="A3:C6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="3" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="3" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="4" t="e">
+      <c r="B7" s="5"/>
+      <c r="C7" s="3" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="3" t="e">
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -1062,45 +1628,136 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05BBDD14-9991-48E3-8F8A-775099A47D61}">
-  <dimension ref="A3:C6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D76E8D2E-3155-4156-882D-9AB79C6F3B6F}">
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="5"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05BBDD14-9991-48E3-8F8A-775099A47D61}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="3" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="3" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="4" t="e">
+      <c r="B7" s="5"/>
+      <c r="C7" s="3" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="3" t="e">
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -1109,34 +1766,34 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4537341F-E850-411C-AD98-9816BDE23BB3}">
   <dimension ref="A3:B5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="B4" s="8"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="B5" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1144,6 +1801,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e238f3b-cf1c-4dc8-b1c3-14677632393c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb274a4b-4ecf-4ae2-a446-66548455045d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100D7FFFCF5F95BC94D9B7DF34B9D0CF76C" ma:contentTypeVersion="15" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="a8184ac6384f947bbc55bc4d9e1749d1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5e238f3b-cf1c-4dc8-b1c3-14677632393c" xmlns:ns3="a7360a35-2516-4210-888a-7cc8dd0a384d" xmlns:ns4="fb274a4b-4ecf-4ae2-a446-66548455045d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6dc33f40212c2dffa236803017f7661f" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="5e238f3b-cf1c-4dc8-b1c3-14677632393c"/>
@@ -1383,27 +2060,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e238f3b-cf1c-4dc8-b1c3-14677632393c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb274a4b-4ecf-4ae2-a446-66548455045d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C25DC3E-57ED-4CB1-BB3F-A437A2199860}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10038610-FC0E-4438-92ED-50D46C596A94}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5e238f3b-cf1c-4dc8-b1c3-14677632393c"/>
+    <ds:schemaRef ds:uri="fb274a4b-4ecf-4ae2-a446-66548455045d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3181E807-AA15-40C5-8B70-A01DB7520019}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1421,23 +2097,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10038610-FC0E-4438-92ED-50D46C596A94}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="5e238f3b-cf1c-4dc8-b1c3-14677632393c"/>
-    <ds:schemaRef ds:uri="fb274a4b-4ecf-4ae2-a446-66548455045d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C25DC3E-57ED-4CB1-BB3F-A437A2199860}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/django/camac/statistics/config/kt_ag/work-items_service-afb.xlsx
+++ b/django/camac/statistics/config/kt_ag/work-items_service-afb.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E11436B-A41B-4983-AC6E-A1FCA7D705BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D8CA50A-0CD4-4E94-A02C-63FDEDA89451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="22485" windowHeight="20430" tabRatio="816" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6780" yWindow="3030" windowWidth="30960" windowHeight="15510" tabRatio="816" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -21,15 +21,28 @@
     <sheet name="Controlling Rolle Fristgerecht" sheetId="10" r:id="rId6"/>
     <sheet name="Controlling Durchlaufzeit FS" sheetId="11" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="61" r:id="rId8"/>
+    <pivotCache cacheId="125" r:id="rId8"/>
   </pivotCaches>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="33">
   <si>
     <t>Dossier-Nr.</t>
   </si>
@@ -79,12 +92,6 @@
     <t>(Leer)</t>
   </si>
   <si>
-    <t>Gesamt: Anzahl</t>
-  </si>
-  <si>
-    <t>Gesamt: Anteil</t>
-  </si>
-  <si>
     <t>Zeilenbeschriftungen</t>
   </si>
   <si>
@@ -125,6 +132,15 @@
   </si>
   <si>
     <t>Durchschnittliche Durchlaufzeit Aufgaben pro zuständige Person</t>
+  </si>
+  <si>
+    <t>Anzahl abgeschlossene Aufgaben</t>
+  </si>
+  <si>
+    <t>Durchschnittliche Durchlaufzeit pro Fachstelle</t>
+  </si>
+  <si>
+    <t>Frist-und Aufgabenfilter</t>
   </si>
 </sst>
 </file>
@@ -146,6 +162,7 @@
       <b/>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
@@ -189,15 +206,33 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="7">
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
@@ -215,7 +250,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Stoppe Tilo  Extern" refreshedDate="46122.594541666665" missingItemsLimit="0" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="19" xr:uid="{A57ED19D-C755-44C2-B72B-40B118E6169D}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Stoppe Tilo  Extern" refreshedDate="46136.500163773148" missingItemsLimit="0" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="19" xr:uid="{A57ED19D-C755-44C2-B72B-40B118E6169D}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:O1048576" sheet="Data"/>
   </cacheSource>
@@ -611,8 +646,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AD818D30-AE36-4ACB-A861-394F5C307186}" name="PivotTable3" cacheId="61" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:A4" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AD818D30-AE36-4ACB-A861-394F5C307186}" name="PivotTable3" cacheId="125" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A5:A6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="15">
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
@@ -637,7 +672,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Anzahl von Dossier-Nr." fld="0" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Anzahl abgeschlossene Aufgaben" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -652,8 +687,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47A99F71-D715-4130-9576-1DA447D613A1}" name="PivotTable4" cacheId="61" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47A99F71-D715-4130-9576-1DA447D613A1}" name="PivotTable4" cacheId="125" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A5:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -694,7 +729,7 @@
     <dataField name="Mittelwert von Durchlaufzeit" fld="13" subtotal="average" baseField="10" baseItem="0" numFmtId="1"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="0">
+    <format dxfId="4">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -717,8 +752,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{152CAD33-7C43-4DE9-8D77-65A9809A8351}" name="PivotTable5" cacheId="61" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Fristgerecht-Filter">
-  <location ref="A3:E7" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{152CAD33-7C43-4DE9-8D77-65A9809A8351}" name="PivotTable5" cacheId="125" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Fristgerecht-Filter">
+  <location ref="A5:C8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
@@ -757,28 +792,19 @@
       <x/>
     </i>
   </rowItems>
-  <colFields count="2">
+  <colFields count="1">
     <field x="14"/>
-    <field x="-2"/>
   </colFields>
-  <colItems count="4">
+  <colItems count="2">
     <i>
       <x/>
-      <x/>
-    </i>
-    <i r="1" i="1">
-      <x v="1"/>
     </i>
     <i t="grand">
       <x/>
     </i>
-    <i t="grand" i="1">
-      <x/>
-    </i>
   </colItems>
-  <dataFields count="2">
+  <dataFields count="1">
     <dataField name="Anzahl" fld="0" subtotal="count" baseField="10" baseItem="0"/>
-    <dataField name="Anteil" fld="0" subtotal="count" showDataAs="percentOfRow" baseField="10" baseItem="0" numFmtId="10"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -793,8 +819,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C25041AB-465F-4D59-A0D5-A4DCE7C22BCC}" name="PivotTable1" cacheId="61" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Fristgerecht-Filter">
-  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C25041AB-465F-4D59-A0D5-A4DCE7C22BCC}" name="PivotTable1" cacheId="125" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Frist-und Aufgabenfilter">
+  <location ref="A5:B9" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
     <pivotField showAll="0" defaultSubtotal="0"/>
@@ -861,8 +887,76 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C35527E3-4E41-4635-ACA8-0C5A7744445B}" name="PivotTable6" cacheId="61" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Rolle" colHeaderCaption="Fristgerecht-Filter">
-  <location ref="A3:E7" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4600EC44-62F3-4435-955C-85186BE745A1}" name="PivotTable2" cacheId="125" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Frist-und Aufgabenfilter">
+  <location ref="A30:B34" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
+  <pivotFields count="15">
+    <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisCol" showAll="0" defaultSubtotal="0">
+      <items count="1">
+        <item x="0"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisRow" showAll="0" defaultSubtotal="0">
+      <items count="1">
+        <item x="0"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisCol" showAll="0" defaultSubtotal="0">
+      <items count="1">
+        <item x="0"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="10"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="2">
+    <field x="14"/>
+    <field x="6"/>
+  </colFields>
+  <colItems count="1">
+    <i>
+      <x/>
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Anzahl von Dossier-Nr." fld="0" subtotal="count" showDataAs="percentOfRow" baseField="10" baseItem="1" numFmtId="10"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FB42A912-6B73-470A-8FF3-10598728C1BF}" name="PivotTable4" cacheId="125" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Rolle" colHeaderCaption="Fristgerecht-Filter">
+  <location ref="J5:L8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
@@ -875,7 +969,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
       <items count="2">
         <item x="0"/>
         <item t="default"/>
@@ -901,27 +995,18 @@
       <x/>
     </i>
   </rowItems>
-  <colFields count="2">
+  <colFields count="1">
     <field x="14"/>
-    <field x="-2"/>
   </colFields>
-  <colItems count="4">
+  <colItems count="2">
     <i>
       <x/>
-      <x/>
-    </i>
-    <i r="1" i="1">
-      <x v="1"/>
     </i>
     <i t="grand">
       <x/>
     </i>
-    <i t="grand" i="1">
-      <x/>
-    </i>
   </colItems>
-  <dataFields count="2">
-    <dataField name="Anzahl" fld="0" subtotal="count" baseField="11" baseItem="0"/>
+  <dataFields count="1">
     <dataField name="Anteil" fld="0" subtotal="count" showDataAs="percentOfRow" baseField="11" baseItem="0" numFmtId="10"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -936,9 +1021,76 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{920585A1-89C8-48F8-85AC-53EA3CF3C46A}" name="PivotTable7" cacheId="61" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Rolle">
-  <location ref="A3:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C35527E3-4E41-4635-ACA8-0C5A7744445B}" name="PivotTable6" cacheId="125" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Rolle" colHeaderCaption="Fristgerecht-Filter">
+  <location ref="A5:C8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="15">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="11"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="14"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Anzahl" fld="0" subtotal="count" baseField="11" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{920585A1-89C8-48F8-85AC-53EA3CF3C46A}" name="PivotTable7" cacheId="125" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Rolle">
+  <location ref="A5:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -1375,112 +1527,112 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
+      <c r="D2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
+      <c r="D3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
+      <c r="D4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
+      <c r="D5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
+      <c r="D6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
+      <c r="D7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
+      <c r="D8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
+      <c r="D9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
+      <c r="D10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
+      <c r="D11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
+      <c r="D12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
+      <c r="D13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
+      <c r="D14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
+      <c r="D15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
+      <c r="D16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
     </row>
     <row r="17" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
+      <c r="D17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
     </row>
     <row r="18" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
+      <c r="D18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
     </row>
     <row r="19" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
+      <c r="D19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -1490,19 +1642,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3455FF73-A558-427D-B009-0D5A326FE23B}">
-  <dimension ref="A3:A4"/>
+  <dimension ref="A5:A6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1511,7 +1663,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6568A324-175D-4B52-B017-796124AF40DD}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -1519,29 +1671,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A1" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
         <v>18</v>
       </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="8"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="8"/>
+      <c r="B6" s="7"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1550,77 +1702,57 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FDB89C4-4A7C-4379-BAAC-67A7DE22B254}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+      <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="C6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="3" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="3" t="e">
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="3" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="3" t="e">
-        <v>#DIV/0!</v>
-      </c>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1629,58 +1761,95 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D76E8D2E-3155-4156-882D-9AB79C6F3B6F}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" customWidth="1"/>
+    <col min="8" max="8" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>15</v>
+      <c r="A1" s="6" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="5"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="8"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="8"/>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="5"/>
+      <c r="B30" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" s="3" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" s="3" t="e">
+        <v>#DIV/0!</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1689,75 +1858,94 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05BBDD14-9991-48E3-8F8A-775099A47D61}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.5703125" customWidth="1"/>
+    <col min="14" max="14" width="17.5703125" customWidth="1"/>
+    <col min="15" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
+    <row r="1" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="C6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="J6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="3" t="e">
+      <c r="L6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="J7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K7" s="3" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="3" t="e">
+      <c r="L7" s="3" t="e">
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="3" t="e">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="J8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" s="3" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="3" t="e">
+      <c r="L8" s="3" t="e">
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -1768,32 +1956,37 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4537341F-E850-411C-AD98-9816BDE23BB3}">
-  <dimension ref="A3:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="8"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="8"/>
+      <c r="B6" s="7"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -1801,26 +1994,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e238f3b-cf1c-4dc8-b1c3-14677632393c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb274a4b-4ecf-4ae2-a446-66548455045d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100D7FFFCF5F95BC94D9B7DF34B9D0CF76C" ma:contentTypeVersion="15" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="a8184ac6384f947bbc55bc4d9e1749d1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5e238f3b-cf1c-4dc8-b1c3-14677632393c" xmlns:ns3="a7360a35-2516-4210-888a-7cc8dd0a384d" xmlns:ns4="fb274a4b-4ecf-4ae2-a446-66548455045d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6dc33f40212c2dffa236803017f7661f" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="5e238f3b-cf1c-4dc8-b1c3-14677632393c"/>
@@ -2060,26 +2233,27 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e238f3b-cf1c-4dc8-b1c3-14677632393c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb274a4b-4ecf-4ae2-a446-66548455045d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C25DC3E-57ED-4CB1-BB3F-A437A2199860}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10038610-FC0E-4438-92ED-50D46C596A94}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="5e238f3b-cf1c-4dc8-b1c3-14677632393c"/>
-    <ds:schemaRef ds:uri="fb274a4b-4ecf-4ae2-a446-66548455045d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3181E807-AA15-40C5-8B70-A01DB7520019}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2097,4 +2271,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10038610-FC0E-4438-92ED-50D46C596A94}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5e238f3b-cf1c-4dc8-b1c3-14677632393c"/>
+    <ds:schemaRef ds:uri="fb274a4b-4ecf-4ae2-a446-66548455045d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C25DC3E-57ED-4CB1-BB3F-A437A2199860}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/django/camac/statistics/config/kt_ag/work-items_service-afb.xlsx
+++ b/django/camac/statistics/config/kt_ag/work-items_service-afb.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D8CA50A-0CD4-4E94-A02C-63FDEDA89451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33FFFA77-99BE-4A60-8856-371893F12FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6780" yWindow="3030" windowWidth="30960" windowHeight="15510" tabRatio="816" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="33105" windowHeight="17610" tabRatio="816" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="125" r:id="rId8"/>
+    <pivotCache cacheId="7" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -214,22 +214,7 @@
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <alignment horizontal="right"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
@@ -250,7 +235,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Stoppe Tilo  Extern" refreshedDate="46136.500163773148" missingItemsLimit="0" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="19" xr:uid="{A57ED19D-C755-44C2-B72B-40B118E6169D}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Stoppe Tilo  Extern" refreshedDate="46146.421274305554" missingItemsLimit="0" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="19" xr:uid="{A57ED19D-C755-44C2-B72B-40B118E6169D}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:O1048576" sheet="Data"/>
   </cacheSource>
@@ -646,7 +631,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AD818D30-AE36-4ACB-A861-394F5C307186}" name="PivotTable3" cacheId="125" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AD818D30-AE36-4ACB-A861-394F5C307186}" name="PivotTable3" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A5:A6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="15">
     <pivotField dataField="1" showAll="0"/>
@@ -687,7 +672,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47A99F71-D715-4130-9576-1DA447D613A1}" name="PivotTable4" cacheId="125" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47A99F71-D715-4130-9576-1DA447D613A1}" name="PivotTable4" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A5:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -729,7 +714,7 @@
     <dataField name="Mittelwert von Durchlaufzeit" fld="13" subtotal="average" baseField="10" baseItem="0" numFmtId="1"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="4">
+    <format dxfId="1">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -752,7 +737,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{152CAD33-7C43-4DE9-8D77-65A9809A8351}" name="PivotTable5" cacheId="125" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Fristgerecht-Filter">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{152CAD33-7C43-4DE9-8D77-65A9809A8351}" name="PivotTable5" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Fristgerecht-Filter">
   <location ref="A5:C8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField dataField="1" showAll="0"/>
@@ -819,8 +804,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C25041AB-465F-4D59-A0D5-A4DCE7C22BCC}" name="PivotTable1" cacheId="125" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Frist-und Aufgabenfilter">
-  <location ref="A5:B9" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4600EC44-62F3-4435-955C-85186BE745A1}" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Frist-und Aufgabenfilter">
+  <location ref="J5:K9" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
     <pivotField showAll="0" defaultSubtotal="0"/>
@@ -836,7 +821,7 @@
     <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisRow" showAll="0" defaultSubtotal="0">
+    <pivotField axis="axisRow" showAll="0" sortType="ascending" defaultSubtotal="0">
       <items count="1">
         <item x="0"/>
       </items>
@@ -872,7 +857,7 @@
     </i>
   </colItems>
   <dataFields count="1">
-    <dataField name="Anzahl Dossiers" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Anzahl von Dossier-Nr." fld="0" subtotal="count" showDataAs="percentOfRow" baseField="10" baseItem="1" numFmtId="10"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -887,8 +872,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4600EC44-62F3-4435-955C-85186BE745A1}" name="PivotTable2" cacheId="125" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Frist-und Aufgabenfilter">
-  <location ref="A30:B34" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C25041AB-465F-4D59-A0D5-A4DCE7C22BCC}" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Frist-und Aufgabenfilter">
+  <location ref="A5:B9" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
     <pivotField showAll="0" defaultSubtotal="0"/>
@@ -904,7 +889,7 @@
     <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisRow" showAll="0" defaultSubtotal="0">
+    <pivotField axis="axisRow" showAll="0" sortType="ascending" defaultSubtotal="0">
       <items count="1">
         <item x="0"/>
       </items>
@@ -940,7 +925,7 @@
     </i>
   </colItems>
   <dataFields count="1">
-    <dataField name="Anzahl von Dossier-Nr." fld="0" subtotal="count" showDataAs="percentOfRow" baseField="10" baseItem="1" numFmtId="10"/>
+    <dataField name="Anzahl Dossiers" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -955,7 +940,74 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FB42A912-6B73-470A-8FF3-10598728C1BF}" name="PivotTable4" cacheId="125" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Rolle" colHeaderCaption="Fristgerecht-Filter">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C35527E3-4E41-4635-ACA8-0C5A7744445B}" name="PivotTable6" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Rolle" colHeaderCaption="Fristgerecht-Filter">
+  <location ref="A5:C8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="15">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="11"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="14"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Anzahl" fld="0" subtotal="count" baseField="11" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FB42A912-6B73-470A-8FF3-10598728C1BF}" name="PivotTable4" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Rolle" colHeaderCaption="Fristgerecht-Filter">
   <location ref="J5:L8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField dataField="1" showAll="0"/>
@@ -1021,75 +1073,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C35527E3-4E41-4635-ACA8-0C5A7744445B}" name="PivotTable6" cacheId="125" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Rolle" colHeaderCaption="Fristgerecht-Filter">
-  <location ref="A5:C8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="15">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="ascending">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="11"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="14"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Anzahl" fld="0" subtotal="count" baseField="11" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{920585A1-89C8-48F8-85AC-53EA3CF3C46A}" name="PivotTable7" cacheId="125" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Rolle">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{920585A1-89C8-48F8-85AC-53EA3CF3C46A}" name="PivotTable7" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Rolle">
   <location ref="A5:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -1761,10 +1746,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D76E8D2E-3155-4156-882D-9AB79C6F3B6F}">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.140625" bestFit="1" customWidth="1"/>
@@ -1773,81 +1758,72 @@
     <col min="7" max="7" width="14.85546875" customWidth="1"/>
     <col min="8" max="8" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="J5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="K6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="J7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="8"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="J8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K8" s="3" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="8"/>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B32" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" s="3" t="e">
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B34" s="3" t="e">
+      <c r="K9" s="3" t="e">
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2234,6 +2210,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e238f3b-cf1c-4dc8-b1c3-14677632393c">
@@ -2242,15 +2227,6 @@
     <TaxCatchAll xmlns="fb274a4b-4ecf-4ae2-a446-66548455045d" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2274,6 +2250,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C25DC3E-57ED-4CB1-BB3F-A437A2199860}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10038610-FC0E-4438-92ED-50D46C596A94}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -2282,12 +2266,4 @@
     <ds:schemaRef ds:uri="fb274a4b-4ecf-4ae2-a446-66548455045d"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C25DC3E-57ED-4CB1-BB3F-A437A2199860}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/django/camac/statistics/config/kt_ag/work-items_service-afb.xlsx
+++ b/django/camac/statistics/config/kt_ag/work-items_service-afb.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33FFFA77-99BE-4A60-8856-371893F12FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9672EC8-0B5B-4193-B0ED-6A25DE1E7EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="33105" windowHeight="17610" tabRatio="816" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="7" r:id="rId8"/>
+    <pivotCache cacheId="15" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="34">
   <si>
     <t>Dossier-Nr.</t>
   </si>
@@ -141,6 +141,9 @@
   </si>
   <si>
     <t>Frist-und Aufgabenfilter</t>
+  </si>
+  <si>
+    <t>Fristgerecht: 0 = nicht fristgerecht, 1 = fristgerecht</t>
   </si>
 </sst>
 </file>
@@ -150,7 +153,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -177,6 +180,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -198,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -210,6 +221,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -235,7 +247,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Stoppe Tilo  Extern" refreshedDate="46146.421274305554" missingItemsLimit="0" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="19" xr:uid="{A57ED19D-C755-44C2-B72B-40B118E6169D}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Stoppe Tilo  Extern" refreshedDate="46146.645671296297" missingItemsLimit="0" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="19" xr:uid="{A57ED19D-C755-44C2-B72B-40B118E6169D}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:O1048576" sheet="Data"/>
   </cacheSource>
@@ -631,7 +643,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AD818D30-AE36-4ACB-A861-394F5C307186}" name="PivotTable3" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AD818D30-AE36-4ACB-A861-394F5C307186}" name="PivotTable3" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A5:A6" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="15">
     <pivotField dataField="1" showAll="0"/>
@@ -672,7 +684,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47A99F71-D715-4130-9576-1DA447D613A1}" name="PivotTable4" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47A99F71-D715-4130-9576-1DA447D613A1}" name="PivotTable4" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A5:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -737,7 +749,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{152CAD33-7C43-4DE9-8D77-65A9809A8351}" name="PivotTable5" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Fristgerecht-Filter">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{152CAD33-7C43-4DE9-8D77-65A9809A8351}" name="PivotTable5" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Fristgerecht-Filter">
   <location ref="A5:C8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField dataField="1" showAll="0"/>
@@ -804,7 +816,75 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4600EC44-62F3-4435-955C-85186BE745A1}" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Frist-und Aufgabenfilter">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C25041AB-465F-4D59-A0D5-A4DCE7C22BCC}" name="PivotTable1" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Frist-und Aufgabenfilter">
+  <location ref="A5:B9" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
+  <pivotFields count="15">
+    <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisCol" showAll="0" defaultSubtotal="0">
+      <items count="1">
+        <item x="0"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="ascending" defaultSubtotal="0">
+      <items count="1">
+        <item x="0"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisCol" showAll="0" defaultSubtotal="0">
+      <items count="1">
+        <item x="0"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="10"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="2">
+    <field x="14"/>
+    <field x="6"/>
+  </colFields>
+  <colItems count="1">
+    <i>
+      <x/>
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Anzahl Dossiers" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4600EC44-62F3-4435-955C-85186BE745A1}" name="PivotTable2" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Frist-und Aufgabenfilter">
   <location ref="J5:K9" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
@@ -871,40 +951,38 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C25041AB-465F-4D59-A0D5-A4DCE7C22BCC}" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Zuständige Person" colHeaderCaption="Frist-und Aufgabenfilter">
-  <location ref="A5:B9" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FB42A912-6B73-470A-8FF3-10598728C1BF}" name="PivotTable4" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Rolle" colHeaderCaption="Fristgerecht-Filter">
+  <location ref="J5:L8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="15">
-    <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisCol" showAll="0" defaultSubtotal="0">
-      <items count="1">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
+      <items count="2">
         <item x="0"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="ascending" defaultSubtotal="0">
-      <items count="1">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="2">
         <item x="0"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisCol" showAll="0" defaultSubtotal="0">
-      <items count="1">
-        <item x="0"/>
+        <item t="default"/>
       </items>
     </pivotField>
   </pivotFields>
   <rowFields count="1">
-    <field x="10"/>
+    <field x="11"/>
   </rowFields>
   <rowItems count="2">
     <i>
@@ -914,18 +992,19 @@
       <x/>
     </i>
   </rowItems>
-  <colFields count="2">
+  <colFields count="1">
     <field x="14"/>
-    <field x="6"/>
   </colFields>
-  <colItems count="1">
+  <colItems count="2">
     <i>
       <x/>
+    </i>
+    <i t="grand">
       <x/>
     </i>
   </colItems>
   <dataFields count="1">
-    <dataField name="Anzahl Dossiers" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Anteil" fld="0" subtotal="count" showDataAs="percentOfRow" baseField="11" baseItem="0" numFmtId="10"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -933,14 +1012,14 @@
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
     </ext>
     <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+      <xpdl:pivotTableDefinition16/>
     </ext>
   </extLst>
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C35527E3-4E41-4635-ACA8-0C5A7744445B}" name="PivotTable6" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Rolle" colHeaderCaption="Fristgerecht-Filter">
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C35527E3-4E41-4635-ACA8-0C5A7744445B}" name="PivotTable6" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Rolle" colHeaderCaption="Fristgerecht-Filter">
   <location ref="A5:C8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField dataField="1" showAll="0"/>
@@ -1006,75 +1085,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FB42A912-6B73-470A-8FF3-10598728C1BF}" name="PivotTable4" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Rolle" colHeaderCaption="Fristgerecht-Filter">
-  <location ref="J5:L8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="15">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="ascending">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="11"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="14"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Anteil" fld="0" subtotal="count" showDataAs="percentOfRow" baseField="11" baseItem="0" numFmtId="10"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{920585A1-89C8-48F8-85AC-53EA3CF3C46A}" name="PivotTable7" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Rolle">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{920585A1-89C8-48F8-85AC-53EA3CF3C46A}" name="PivotTable7" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Rolle">
   <location ref="A5:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -1687,7 +1699,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FDB89C4-4A7C-4379-BAAC-67A7DE22B254}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
@@ -1701,12 +1713,15 @@
     <col min="9" max="9" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="H1" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>20</v>
       </c>
@@ -1714,7 +1729,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -1725,14 +1740,14 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -1765,6 +1780,9 @@
     <row r="1" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>27</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -1858,6 +1876,9 @@
       <c r="A1" s="6" t="s">
         <v>25</v>
       </c>
+      <c r="H1" s="9" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -1970,6 +1991,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e238f3b-cf1c-4dc8-b1c3-14677632393c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb274a4b-4ecf-4ae2-a446-66548455045d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100D7FFFCF5F95BC94D9B7DF34B9D0CF76C" ma:contentTypeVersion="15" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="a8184ac6384f947bbc55bc4d9e1749d1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5e238f3b-cf1c-4dc8-b1c3-14677632393c" xmlns:ns3="a7360a35-2516-4210-888a-7cc8dd0a384d" xmlns:ns4="fb274a4b-4ecf-4ae2-a446-66548455045d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6dc33f40212c2dffa236803017f7661f" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="5e238f3b-cf1c-4dc8-b1c3-14677632393c"/>
@@ -2209,27 +2250,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e238f3b-cf1c-4dc8-b1c3-14677632393c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb274a4b-4ecf-4ae2-a446-66548455045d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10038610-FC0E-4438-92ED-50D46C596A94}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5e238f3b-cf1c-4dc8-b1c3-14677632393c"/>
+    <ds:schemaRef ds:uri="fb274a4b-4ecf-4ae2-a446-66548455045d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C25DC3E-57ED-4CB1-BB3F-A437A2199860}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3181E807-AA15-40C5-8B70-A01DB7520019}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2247,23 +2287,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C25DC3E-57ED-4CB1-BB3F-A437A2199860}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10038610-FC0E-4438-92ED-50D46C596A94}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="5e238f3b-cf1c-4dc8-b1c3-14677632393c"/>
-    <ds:schemaRef ds:uri="fb274a4b-4ecf-4ae2-a446-66548455045d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>